--- a/_data/syllabus.xlsx
+++ b/_data/syllabus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17743\Desktop\syllabus_template\_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17743\Desktop\MMAElectronics\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2703D64-1EE0-4ED0-AA6B-F867032BF849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1079BE-1829-402E-9009-05B3A3FBAA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="60" windowWidth="16785" windowHeight="15330" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -605,7 +604,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>44811</v>
+        <v>46085</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -622,7 +621,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>44813</v>
+        <v>46087</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -639,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>44816</v>
+        <v>46090</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -656,7 +655,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>44818</v>
+        <v>46092</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -673,7 +672,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>44820</v>
+        <v>46094</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -690,7 +689,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>44823</v>
+        <v>46097</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -707,7 +706,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>44825</v>
+        <v>46099</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -724,7 +723,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>44827</v>
+        <v>46101</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -738,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>44830</v>
+        <v>46104</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -755,7 +754,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>44832</v>
+        <v>46078</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -772,7 +771,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>44834</v>
+        <v>46108</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -789,7 +788,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>44837</v>
+        <v>46111</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -806,7 +805,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>44839</v>
+        <v>46113</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -823,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>44841</v>
+        <v>46115</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -840,7 +839,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>44845</v>
+        <v>46118</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -857,7 +856,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>44846</v>
+        <v>46120</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -874,7 +873,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>44848</v>
+        <v>46122</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -888,7 +887,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>44851</v>
+        <v>46125</v>
       </c>
       <c r="C19">
         <v>7</v>
@@ -902,7 +901,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>44853</v>
+        <v>46127</v>
       </c>
       <c r="C20">
         <v>7</v>
@@ -916,7 +915,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>44855</v>
+        <v>46134</v>
       </c>
       <c r="C21">
         <v>7</v>
@@ -930,7 +929,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>44858</v>
+        <v>46136</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -947,7 +946,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>44860</v>
+        <v>46139</v>
       </c>
       <c r="C23">
         <v>8</v>
@@ -964,7 +963,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>44862</v>
+        <v>46141</v>
       </c>
       <c r="C24">
         <v>8</v>
@@ -981,7 +980,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>44865</v>
+        <v>46143</v>
       </c>
       <c r="C25">
         <v>9</v>
@@ -998,7 +997,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>44867</v>
+        <v>46146</v>
       </c>
       <c r="C26">
         <v>9</v>
@@ -1015,7 +1014,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>44869</v>
+        <v>46148</v>
       </c>
       <c r="C27">
         <v>9</v>
@@ -1029,7 +1028,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>44872</v>
+        <v>46150</v>
       </c>
       <c r="C28">
         <v>10</v>
@@ -1046,7 +1045,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>44874</v>
+        <v>46153</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -1063,7 +1062,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>44879</v>
+        <v>46155</v>
       </c>
       <c r="C30">
         <v>11</v>
@@ -1080,7 +1079,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>44881</v>
+        <v>46157</v>
       </c>
       <c r="C31">
         <v>11</v>
@@ -1097,7 +1096,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>44883</v>
+        <v>46160</v>
       </c>
       <c r="C32">
         <v>11</v>
@@ -1114,7 +1113,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>44886</v>
+        <v>46162</v>
       </c>
       <c r="C33">
         <v>12</v>
@@ -1128,7 +1127,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="1">
-        <v>44893</v>
+        <v>46164</v>
       </c>
       <c r="C34">
         <v>13</v>
@@ -1145,7 +1144,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="1">
-        <v>44895</v>
+        <v>46168</v>
       </c>
       <c r="C35">
         <v>13</v>
@@ -1162,7 +1161,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="1">
-        <v>44897</v>
+        <v>46169</v>
       </c>
       <c r="C36">
         <v>13</v>
@@ -1179,7 +1178,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="1">
-        <v>44900</v>
+        <v>46171</v>
       </c>
       <c r="C37">
         <v>14</v>
@@ -1196,7 +1195,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="1">
-        <v>44902</v>
+        <v>46174</v>
       </c>
       <c r="C38">
         <v>14</v>
@@ -1213,7 +1212,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>44904</v>
+        <v>46176</v>
       </c>
       <c r="C39">
         <v>14</v>
@@ -1227,7 +1226,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>44907</v>
+        <v>46178</v>
       </c>
       <c r="C40">
         <v>15</v>
@@ -1241,7 +1240,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="1">
-        <v>44909</v>
+        <v>46181</v>
       </c>
       <c r="C41">
         <v>15</v>

--- a/_data/syllabus.xlsx
+++ b/_data/syllabus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17743\Desktop\MMAElectronics\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1079BE-1829-402E-9009-05B3A3FBAA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13595F9-6794-467D-8189-659969677344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
   </bookViews>

--- a/_data/syllabus.xlsx
+++ b/_data/syllabus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17743\Desktop\MMAElectronics\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13595F9-6794-467D-8189-659969677344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961A8029-EEEF-44A5-A389-6195B8304562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
+    <workbookView xWindow="0" yWindow="120" windowWidth="18570" windowHeight="15285" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
   <si>
     <t>Lesson_Title</t>
   </si>
@@ -64,141 +64,6 @@
     <t>Final Review</t>
   </si>
   <si>
-    <t>ZyBook Reading</t>
-  </si>
-  <si>
-    <t>1.1, 1.2</t>
-  </si>
-  <si>
-    <t>Basic Electricity: Introduction / Electricity and Magnatism</t>
-  </si>
-  <si>
-    <t>Basic Electricity: Current / Voltage / Energy and Power / Resistors</t>
-  </si>
-  <si>
-    <t>1.3 - 1.6</t>
-  </si>
-  <si>
-    <t>Basic Electricity: Ohm's Law / Voltage Sources / Current Sources / Switches / Simple Circuits</t>
-  </si>
-  <si>
-    <t>1.7 - 1.11</t>
-  </si>
-  <si>
-    <t>Basic Electricity: Capacitors / Inductors / Nonlinear Voltage and Current Sources / Safety</t>
-  </si>
-  <si>
-    <t>1.12 - 1.16</t>
-  </si>
-  <si>
-    <t>Resistor Networks: Conductance / Kirchhoff's Voltage Law</t>
-  </si>
-  <si>
-    <t>2.1, 2.2</t>
-  </si>
-  <si>
-    <t>3.2, 3.3</t>
-  </si>
-  <si>
-    <t>Resistor Networks: Series and Parallel / Voltage Divider</t>
-  </si>
-  <si>
-    <t>2.3, 2.4</t>
-  </si>
-  <si>
-    <t>Resistor Networks: Kirchhoff's Current Law / Current divider</t>
-  </si>
-  <si>
-    <t>2.5, 2.6</t>
-  </si>
-  <si>
-    <t>Resistor Networks: Parallel Series Analysis / Additional Topics</t>
-  </si>
-  <si>
-    <t>2.7, 2.8</t>
-  </si>
-  <si>
-    <t>2.9 - 2.11</t>
-  </si>
-  <si>
-    <t>Network Analysis: Superposition and Linearity</t>
-  </si>
-  <si>
-    <t>Network Analysis: Node Analysis / Mesh Analysis</t>
-  </si>
-  <si>
-    <t>Network Analysis: Thevenin Equivalent / Norton Equivalent / Source Transformations</t>
-  </si>
-  <si>
-    <t>3.4 - 3.6</t>
-  </si>
-  <si>
-    <t>Semester Summary: WSB Temperature Sensor / After Exam 1</t>
-  </si>
-  <si>
-    <t>Frequency - Domain Analysis: Sinusoidal Steady State / Complex numbers / Euler's formula</t>
-  </si>
-  <si>
-    <t>Frequency - Domain Analysis: Resistor, Capcitor, and Inductor Impedance</t>
-  </si>
-  <si>
-    <t>5.2 - 5.4</t>
-  </si>
-  <si>
-    <t>Frequency - Domain Analysis: Admittance / First - Order Frequency Response</t>
-  </si>
-  <si>
-    <t>5.5, 5.6</t>
-  </si>
-  <si>
-    <t>Frequency - Domain Analysis: Phasors / RMS Voltages and Currents</t>
-  </si>
-  <si>
-    <t>5.10, 5.11</t>
-  </si>
-  <si>
-    <t>Frequency - Domain Analysis: Reactive Power / Complex Power / Power Factor Correction</t>
-  </si>
-  <si>
-    <t>5.12 - 5.14</t>
-  </si>
-  <si>
-    <t>Op - Amps: Ideal Op - Amps / Feedback</t>
-  </si>
-  <si>
-    <t>6.2, 6.3</t>
-  </si>
-  <si>
-    <t>Op - Amps: Inverting Amplifier / Noninverting Amplifier / Integrator and Differentiator</t>
-  </si>
-  <si>
-    <t>6.4 - 6.6</t>
-  </si>
-  <si>
-    <t>Op - Amps: Practical Op - Amps</t>
-  </si>
-  <si>
-    <t>Op - Amps: Multiple Op - Amp Circuits</t>
-  </si>
-  <si>
-    <t>Combinational Logic: Electronics and Digital Systems / Gates</t>
-  </si>
-  <si>
-    <t>Combinational Logic: Boolean Algebra and Equations</t>
-  </si>
-  <si>
-    <t>7.1, 7.2</t>
-  </si>
-  <si>
-    <t>Combinational Logic: Equations to/from Circuits</t>
-  </si>
-  <si>
-    <t>Combinational Logic: Two - Level Combinational Logic Simplification</t>
-  </si>
-  <si>
-    <t>Combinational Logic: Demorgan's Law</t>
-  </si>
-  <si>
     <t>Homework</t>
   </si>
   <si>
@@ -212,6 +77,96 @@
   </si>
   <si>
     <t>Due Date</t>
+  </si>
+  <si>
+    <t>Introduction: Syllabus / Overview</t>
+  </si>
+  <si>
+    <t>Review: Definitions / Ohm's Law / Kirchhoff's Laws</t>
+  </si>
+  <si>
+    <t>DC Analysis: Series / Parallel / Voltage Divider / Current Divider</t>
+  </si>
+  <si>
+    <t>DC Analysis: Combine Series Parallel Circuits</t>
+  </si>
+  <si>
+    <t>DC Analysis: Application WSB</t>
+  </si>
+  <si>
+    <t>DC Analysis: Grouns and Commons</t>
+  </si>
+  <si>
+    <t>DC Analysis: Superposition and Linearity</t>
+  </si>
+  <si>
+    <t>Complex Numbers: Basic Operations</t>
+  </si>
+  <si>
+    <t>AC Analysis: Complex Impedance</t>
+  </si>
+  <si>
+    <t>AC Analysis: Circuit Analysis Part 1</t>
+  </si>
+  <si>
+    <t>AC Analysis: Circuit Analysis Part 2</t>
+  </si>
+  <si>
+    <t>Frequency Domain: Introduction Fourier Transform Discussion</t>
+  </si>
+  <si>
+    <t>Frequency Domain: Resonance</t>
+  </si>
+  <si>
+    <t>Frequency Domain: Filters</t>
+  </si>
+  <si>
+    <t>Frequency Domain: Frequency Response Functions Part 1</t>
+  </si>
+  <si>
+    <t>Frequency Domain: Frequency Response Functions Part 2</t>
+  </si>
+  <si>
+    <t>Solid State Devices: Introduction PN junctions / Diodes</t>
+  </si>
+  <si>
+    <t>Solid State Devices: Transistors / NPN Bipolar Junction Transistors</t>
+  </si>
+  <si>
+    <t>Op - Amps: Basic Circuits / Gain</t>
+  </si>
+  <si>
+    <t>Op - Amps: Equation Building 1</t>
+  </si>
+  <si>
+    <t>Op - Amps: Equation Building 2</t>
+  </si>
+  <si>
+    <t>Introduction to Sensors: Part 1 Transfer Functions</t>
+  </si>
+  <si>
+    <t>Introduction to Sensors: Part 2 WSB to Op - Amp Circuit</t>
+  </si>
+  <si>
+    <t>DC Analysis: Node Mesh Analysis</t>
+  </si>
+  <si>
+    <t>DC Analysis: Mesh Analysis</t>
+  </si>
+  <si>
+    <t>Boolean Opperators: Introduction</t>
+  </si>
+  <si>
+    <t>Combinational Logic: Logic Gates</t>
+  </si>
+  <si>
+    <t>Combinational Logic: Circuits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Counting Systems: Introduction / Bin to Dec / Hex to Dec </t>
+  </si>
+  <si>
+    <t>Base Counting Systems: Dec to Bin / Dec to Hex / Hex to Bin / Bin to Hex</t>
   </si>
 </sst>
 </file>
@@ -567,7 +522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6140B2AC-698B-4497-B956-2C117CDF8902}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="15.7109375" customWidth="1"/>
@@ -576,15 +531,15 @@
     <col min="5" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -593,13 +548,10 @@
         <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -610,13 +562,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -627,13 +576,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -644,13 +590,10 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -663,11 +606,8 @@
       <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -678,13 +618,10 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -695,13 +632,10 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -712,13 +646,10 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -732,7 +663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -743,13 +674,10 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -760,13 +688,10 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -777,13 +702,10 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -794,13 +716,10 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -811,13 +730,10 @@
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -828,13 +744,10 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -845,13 +758,10 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -862,13 +772,10 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -879,10 +786,10 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -893,10 +800,10 @@
         <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -907,10 +814,10 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -921,10 +828,10 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -935,13 +842,10 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -952,13 +856,10 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -969,13 +870,10 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -986,13 +884,10 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1003,13 +898,10 @@
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1020,10 +912,10 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1034,13 +926,10 @@
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1051,13 +940,10 @@
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1068,13 +954,10 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1085,13 +968,10 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1102,13 +982,10 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
-      </c>
-      <c r="E32">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1122,7 +999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1133,13 +1010,10 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1150,13 +1024,10 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1167,13 +1038,10 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1184,13 +1052,10 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1201,13 +1066,10 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1221,7 +1083,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1235,7 +1097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>

--- a/_data/syllabus.xlsx
+++ b/_data/syllabus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17743\Desktop\MMAElectronics\_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961A8029-EEEF-44A5-A389-6195B8304562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B45785-67EB-4580-AF7C-BCB9ECEC30E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="120" windowWidth="18570" windowHeight="15285" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
+    <workbookView xWindow="1560" yWindow="915" windowWidth="18570" windowHeight="15285" xr2:uid="{8D30C5C3-6C3E-4333-85B5-3F3AF73458A5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,6 @@
     <t>DC Analysis: Application WSB</t>
   </si>
   <si>
-    <t>DC Analysis: Grouns and Commons</t>
-  </si>
-  <si>
     <t>DC Analysis: Superposition and Linearity</t>
   </si>
   <si>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>Base Counting Systems: Dec to Bin / Dec to Hex / Hex to Bin / Bin to Hex</t>
+  </si>
+  <si>
+    <t>DC Analysis: Grounds and Commons</t>
   </si>
 </sst>
 </file>
@@ -646,7 +646,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -674,7 +674,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -688,7 +688,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -702,7 +702,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -716,7 +716,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,7 +744,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -758,7 +758,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,7 +786,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -828,7 +828,7 @@
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -842,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -856,7 +856,7 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -870,7 +870,7 @@
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -884,7 +884,7 @@
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -912,7 +912,7 @@
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -926,7 +926,7 @@
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -940,7 +940,7 @@
         <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -954,7 +954,7 @@
         <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -968,7 +968,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -982,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1010,7 +1010,7 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1024,7 +1024,7 @@
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1052,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1066,7 +1066,7 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
